--- a/data/raw/paper_01.xlsx
+++ b/data/raw/paper_01.xlsx
@@ -16518,7 +16518,7 @@
         <v>0</v>
       </c>
       <c r="Q302">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="303" spans="1:17" x14ac:dyDescent="0.25">
